--- a/docs/Results/Counties/Bayern/pop_results_Kreisfreie_Stadt_Schwabach_CT_vs_Stroke.xlsx
+++ b/docs/Results/Counties/Bayern/pop_results_Kreisfreie_Stadt_Schwabach_CT_vs_Stroke.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,43 +453,43 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>All Stroke Units</t>
+          <t>Hospitals with CT</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>42132</v>
+        <v>20936</v>
       </c>
       <c r="D2" t="n">
-        <v>100</v>
+        <v>49.69</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>All Stroke Units</t>
+          <t>Hospitals with CT</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C3" t="n">
-        <v>42132</v>
+        <v>41648</v>
       </c>
       <c r="D3" t="n">
-        <v>100</v>
+        <v>98.84999999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>All Stroke Units</t>
+          <t>Hospitals with CT</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="C4" t="n">
         <v>42132</v>
@@ -501,11 +501,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>All Stroke Units</t>
+          <t>Hospitals with CT</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="C5" t="n">
         <v>42132</v>
@@ -521,10 +521,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C6" t="n">
-        <v>42131</v>
+        <v>42132</v>
       </c>
       <c r="D6" t="n">
         <v>100</v>
@@ -553,7 +553,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="C8" t="n">
         <v>42132</v>
@@ -569,12 +569,460 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>40</v>
+      </c>
+      <c r="C9" t="n">
+        <v>42132</v>
+      </c>
+      <c r="D9" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Hospitals with CT</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>45</v>
+      </c>
+      <c r="C10" t="n">
+        <v>42132</v>
+      </c>
+      <c r="D10" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Hospitals with CT</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>50</v>
+      </c>
+      <c r="C11" t="n">
+        <v>42132</v>
+      </c>
+      <c r="D11" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Hospitals with CT</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>55</v>
+      </c>
+      <c r="C12" t="n">
+        <v>42132</v>
+      </c>
+      <c r="D12" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Hospitals with CT</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
         <v>60</v>
       </c>
-      <c r="C9" t="n">
-        <v>42132</v>
-      </c>
-      <c r="D9" t="n">
+      <c r="C13" t="n">
+        <v>42132</v>
+      </c>
+      <c r="D13" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Extended Stroke Hospitals</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C14" t="n">
+        <v>24442</v>
+      </c>
+      <c r="D14" t="n">
+        <v>58.01</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Extended Stroke Hospitals</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>10</v>
+      </c>
+      <c r="C15" t="n">
+        <v>41814</v>
+      </c>
+      <c r="D15" t="n">
+        <v>99.25</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Extended Stroke Hospitals</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>15</v>
+      </c>
+      <c r="C16" t="n">
+        <v>42132</v>
+      </c>
+      <c r="D16" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Extended Stroke Hospitals</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>20</v>
+      </c>
+      <c r="C17" t="n">
+        <v>42132</v>
+      </c>
+      <c r="D17" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Extended Stroke Hospitals</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>25</v>
+      </c>
+      <c r="C18" t="n">
+        <v>42132</v>
+      </c>
+      <c r="D18" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Extended Stroke Hospitals</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>30</v>
+      </c>
+      <c r="C19" t="n">
+        <v>42132</v>
+      </c>
+      <c r="D19" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Extended Stroke Hospitals</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>35</v>
+      </c>
+      <c r="C20" t="n">
+        <v>42132</v>
+      </c>
+      <c r="D20" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Extended Stroke Hospitals</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>40</v>
+      </c>
+      <c r="C21" t="n">
+        <v>42132</v>
+      </c>
+      <c r="D21" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Extended Stroke Hospitals</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>45</v>
+      </c>
+      <c r="C22" t="n">
+        <v>42132</v>
+      </c>
+      <c r="D22" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Extended Stroke Hospitals</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>50</v>
+      </c>
+      <c r="C23" t="n">
+        <v>42132</v>
+      </c>
+      <c r="D23" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Extended Stroke Hospitals</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>55</v>
+      </c>
+      <c r="C24" t="n">
+        <v>42132</v>
+      </c>
+      <c r="D24" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Extended Stroke Hospitals</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>60</v>
+      </c>
+      <c r="C25" t="n">
+        <v>42132</v>
+      </c>
+      <c r="D25" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Stroke Units</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>5</v>
+      </c>
+      <c r="C26" t="n">
+        <v>20387</v>
+      </c>
+      <c r="D26" t="n">
+        <v>48.39</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Stroke Units</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>10</v>
+      </c>
+      <c r="C27" t="n">
+        <v>41672</v>
+      </c>
+      <c r="D27" t="n">
+        <v>98.91</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Stroke Units</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>15</v>
+      </c>
+      <c r="C28" t="n">
+        <v>42132</v>
+      </c>
+      <c r="D28" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Stroke Units</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>20</v>
+      </c>
+      <c r="C29" t="n">
+        <v>42132</v>
+      </c>
+      <c r="D29" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Stroke Units</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>25</v>
+      </c>
+      <c r="C30" t="n">
+        <v>42132</v>
+      </c>
+      <c r="D30" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Stroke Units</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>30</v>
+      </c>
+      <c r="C31" t="n">
+        <v>42132</v>
+      </c>
+      <c r="D31" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Stroke Units</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>35</v>
+      </c>
+      <c r="C32" t="n">
+        <v>42132</v>
+      </c>
+      <c r="D32" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Stroke Units</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>40</v>
+      </c>
+      <c r="C33" t="n">
+        <v>42132</v>
+      </c>
+      <c r="D33" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Stroke Units</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>45</v>
+      </c>
+      <c r="C34" t="n">
+        <v>42132</v>
+      </c>
+      <c r="D34" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Stroke Units</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>50</v>
+      </c>
+      <c r="C35" t="n">
+        <v>42132</v>
+      </c>
+      <c r="D35" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Stroke Units</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>55</v>
+      </c>
+      <c r="C36" t="n">
+        <v>42132</v>
+      </c>
+      <c r="D36" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Stroke Units</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>60</v>
+      </c>
+      <c r="C37" t="n">
+        <v>42132</v>
+      </c>
+      <c r="D37" t="n">
         <v>100</v>
       </c>
     </row>

--- a/docs/Results/Counties/Bayern/pop_results_Kreisfreie_Stadt_Schwabach_CT_vs_Stroke.xlsx
+++ b/docs/Results/Counties/Bayern/pop_results_Kreisfreie_Stadt_Schwabach_CT_vs_Stroke.xlsx
@@ -645,7 +645,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -661,7 +661,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -677,7 +677,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -693,7 +693,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -709,7 +709,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -725,7 +725,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -741,7 +741,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -757,7 +757,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -773,7 +773,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -789,7 +789,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -805,7 +805,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -821,7 +821,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="B25" t="n">
